--- a/resources/tiktok-shop-affiliate/files/ttsa-int-settled-commission-tracker.xlsx
+++ b/resources/tiktok-shop-affiliate/files/ttsa-int-settled-commission-tracker.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -59,11 +59,6 @@
       <color rgb="000C2733"/>
       <sz val="12"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="5">
     <fill>
@@ -114,7 +109,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -172,8 +167,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -539,7 +532,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H139"/>
+  <dimension ref="A1:H137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -587,7 +580,6 @@
         </is>
       </c>
     </row>
-    <row r="6"/>
     <row r="7">
       <c r="A7" s="3" t="inlineStr">
         <is>
@@ -2190,7 +2182,6 @@
         <v/>
       </c>
     </row>
-    <row r="128"/>
     <row r="129">
       <c r="C129" s="10" t="inlineStr">
         <is>
@@ -2213,7 +2204,6 @@
         <v/>
       </c>
     </row>
-    <row r="131"/>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
         <is>
@@ -2235,7 +2225,6 @@
         </is>
       </c>
     </row>
-    <row r="135"/>
     <row r="136">
       <c r="A136" s="2" t="inlineStr">
         <is>
@@ -2246,13 +2235,9 @@
     <row r="137">
       <c r="A137" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global</t>
-        </is>
-      </c>
-    </row>
-    <row r="138"/>
-    <row r="139">
-      <c r="A139" s="24" t="n"/>
+          <t>ePORTS — your ecom source (eports.global)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2321,7 +2306,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
@@ -2630,7 +2614,6 @@
         <v/>
       </c>
     </row>
-    <row r="19"/>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
@@ -2645,7 +2628,6 @@
         </is>
       </c>
     </row>
-    <row r="22"/>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
@@ -2826,7 +2808,6 @@
         <v/>
       </c>
     </row>
-    <row r="38"/>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
@@ -2834,7 +2815,6 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
@@ -2845,7 +2825,7 @@
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
